--- a/Design Files/Dimmer-Board-v1.0/BOM/eSpark-BOM_Dimmer-Board-v1.0.xlsx
+++ b/Design Files/Dimmer-Board-v1.0/BOM/eSpark-BOM_Dimmer-Board-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="103">
   <si>
     <t>Component list</t>
   </si>
@@ -295,6 +295,39 @@
   </si>
   <si>
     <t>-----</t>
+  </si>
+  <si>
+    <t>Peripheral</t>
+  </si>
+  <si>
+    <t>Heatsink</t>
+  </si>
+  <si>
+    <t>35*12*25MM 6063-T5 aluminum Heat sink/heatsink</t>
+  </si>
+  <si>
+    <t>Custom</t>
+  </si>
+  <si>
+    <t>35*12*25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XSD </t>
+  </si>
+  <si>
+    <t>Screw</t>
+  </si>
+  <si>
+    <t>phillips small pan head screw and spring pad combination</t>
+  </si>
+  <si>
+    <t>Tong Ming</t>
+  </si>
+  <si>
+    <t>C4663</t>
+  </si>
+  <si>
+    <t>C5239988</t>
   </si>
 </sst>
 </file>
@@ -474,7 +507,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -600,12 +633,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -710,6 +754,15 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -721,13 +774,7 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1018,7 +1065,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:R33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="10" customWidth="1"/>
@@ -1051,14 +1098,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="45"/>
+      <c r="Q1" s="45"/>
+      <c r="R1" s="45"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1246,7 +1293,7 @@
       <c r="H8" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="I8" s="47" t="s">
+      <c r="I8" s="44" t="s">
         <v>91</v>
       </c>
       <c r="J8" s="14" t="s">
@@ -1265,7 +1312,7 @@
       <c r="N8" s="14">
         <v>20</v>
       </c>
-      <c r="O8" s="45" t="s">
+      <c r="O8" s="42" t="s">
         <v>89</v>
       </c>
       <c r="P8" s="15">
@@ -1280,7 +1327,7 @@
     <row r="9" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="17">
-        <f t="shared" ref="B9:B17" si="0">ROW(B9) - ROW($B$7)</f>
+        <f t="shared" ref="B9:B19" si="0">ROW(B9) - ROW($B$7)</f>
         <v>2</v>
       </c>
       <c r="C9" s="23" t="s">
@@ -1301,7 +1348,7 @@
       <c r="H9" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="I9" s="47" t="s">
+      <c r="I9" s="44" t="s">
         <v>91</v>
       </c>
       <c r="J9" s="20" t="s">
@@ -1320,7 +1367,7 @@
       <c r="N9" s="14">
         <v>6</v>
       </c>
-      <c r="O9" s="45" t="s">
+      <c r="O9" s="42" t="s">
         <v>89</v>
       </c>
       <c r="P9" s="15">
@@ -1356,7 +1403,7 @@
       <c r="H10" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="I10" s="47" t="s">
+      <c r="I10" s="44" t="s">
         <v>91</v>
       </c>
       <c r="J10" s="14" t="s">
@@ -1375,7 +1422,7 @@
       <c r="N10" s="20">
         <v>6</v>
       </c>
-      <c r="O10" s="46" t="s">
+      <c r="O10" s="43" t="s">
         <v>89</v>
       </c>
       <c r="P10" s="21">
@@ -1411,7 +1458,7 @@
       <c r="H11" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="I11" s="47" t="s">
+      <c r="I11" s="44" t="s">
         <v>91</v>
       </c>
       <c r="J11" s="20" t="s">
@@ -1430,7 +1477,7 @@
       <c r="N11" s="14">
         <v>10</v>
       </c>
-      <c r="O11" s="45" t="s">
+      <c r="O11" s="42" t="s">
         <v>89</v>
       </c>
       <c r="P11" s="15">
@@ -1466,7 +1513,7 @@
       <c r="H12" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="I12" s="47" t="s">
+      <c r="I12" s="44" t="s">
         <v>91</v>
       </c>
       <c r="J12" s="14" t="s">
@@ -1485,7 +1532,7 @@
       <c r="N12" s="20">
         <v>50</v>
       </c>
-      <c r="O12" s="46" t="s">
+      <c r="O12" s="43" t="s">
         <v>89</v>
       </c>
       <c r="P12" s="21">
@@ -1521,7 +1568,7 @@
       <c r="H13" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="I13" s="47" t="s">
+      <c r="I13" s="44" t="s">
         <v>91</v>
       </c>
       <c r="J13" s="20" t="s">
@@ -1540,7 +1587,7 @@
       <c r="N13" s="20">
         <v>20</v>
       </c>
-      <c r="O13" s="46" t="s">
+      <c r="O13" s="43" t="s">
         <v>89</v>
       </c>
       <c r="P13" s="21">
@@ -1576,7 +1623,7 @@
       <c r="H14" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="I14" s="47" t="s">
+      <c r="I14" s="44" t="s">
         <v>91</v>
       </c>
       <c r="J14" s="14" t="s">
@@ -1595,7 +1642,7 @@
       <c r="N14" s="14">
         <v>10</v>
       </c>
-      <c r="O14" s="45" t="s">
+      <c r="O14" s="42" t="s">
         <v>89</v>
       </c>
       <c r="P14" s="15">
@@ -1631,7 +1678,7 @@
       <c r="H15" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="I15" s="47" t="s">
+      <c r="I15" s="44" t="s">
         <v>91</v>
       </c>
       <c r="J15" s="20" t="s">
@@ -1650,7 +1697,7 @@
       <c r="N15" s="20">
         <v>10</v>
       </c>
-      <c r="O15" s="46" t="s">
+      <c r="O15" s="43" t="s">
         <v>89</v>
       </c>
       <c r="P15" s="21">
@@ -1686,7 +1733,7 @@
       <c r="H16" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="I16" s="47" t="s">
+      <c r="I16" s="44" t="s">
         <v>91</v>
       </c>
       <c r="J16" s="14" t="s">
@@ -1705,7 +1752,7 @@
       <c r="N16" s="14">
         <v>10</v>
       </c>
-      <c r="O16" s="45" t="s">
+      <c r="O16" s="42" t="s">
         <v>89</v>
       </c>
       <c r="P16" s="15">
@@ -1717,10 +1764,10 @@
       </c>
       <c r="R16" s="14"/>
     </row>
-    <row r="17" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="17">
-        <f t="shared" si="0"/>
+      <c r="B17" s="16">
+        <f>ROW(B17) - ROW($B$7)</f>
         <v>10</v>
       </c>
       <c r="C17" s="23" t="s">
@@ -1741,93 +1788,203 @@
       <c r="H17" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="I17" s="47" t="s">
+      <c r="I17" s="44" t="s">
         <v>91</v>
       </c>
       <c r="J17" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="K17" s="20"/>
+      <c r="K17" s="20" t="s">
+        <v>90</v>
+      </c>
       <c r="L17" s="20">
         <v>1</v>
       </c>
       <c r="M17" s="20">
-        <f t="shared" ref="M17" si="9">L17*5</f>
+        <f t="shared" ref="M17:M19" si="9">L17*5</f>
         <v>5</v>
       </c>
       <c r="N17" s="20">
         <v>6</v>
       </c>
-      <c r="O17" s="46" t="s">
+      <c r="O17" s="43" t="s">
         <v>89</v>
       </c>
       <c r="P17" s="21">
         <v>0.41149999999999998</v>
       </c>
       <c r="Q17" s="21">
-        <f t="shared" ref="Q17" si="10">P17*N17</f>
+        <f t="shared" ref="Q17:Q19" si="10">P17*N17</f>
         <v>2.4689999999999999</v>
       </c>
       <c r="R17" s="20"/>
     </row>
-    <row r="18" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="43" t="s">
+      <c r="B18" s="16">
+        <f>ROW(B18) - ROW($B$7)</f>
+        <v>11</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G18" s="48" t="s">
+        <v>96</v>
+      </c>
+      <c r="H18" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="I18" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="K18" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="L18" s="20">
+        <v>1</v>
+      </c>
+      <c r="M18" s="20">
+        <f t="shared" si="9"/>
+        <v>5</v>
+      </c>
+      <c r="N18" s="20">
+        <v>5</v>
+      </c>
+      <c r="O18" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="P18" s="21">
+        <v>0.2349</v>
+      </c>
+      <c r="Q18" s="21">
+        <f t="shared" si="10"/>
+        <v>1.1745000000000001</v>
+      </c>
+      <c r="R18" s="20"/>
+    </row>
+    <row r="19" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1"/>
+      <c r="B19" s="17">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G19" s="48">
+        <v>266068</v>
+      </c>
+      <c r="H19" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="I19" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20">
+        <v>1</v>
+      </c>
+      <c r="M19" s="20">
+        <f t="shared" si="9"/>
+        <v>5</v>
+      </c>
+      <c r="N19" s="20">
+        <v>50</v>
+      </c>
+      <c r="O19" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="P19" s="21">
+        <v>9.1000000000000004E-3</v>
+      </c>
+      <c r="Q19" s="21">
+        <f t="shared" si="10"/>
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="R19" s="20"/>
+    </row>
+    <row r="20" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="44"/>
-      <c r="P18" s="44"/>
-      <c r="Q18" s="18">
-        <f>SUM(Q8:Q17)</f>
-        <v>34.8598</v>
-      </c>
-      <c r="R18" s="1"/>
-    </row>
-    <row r="19" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="43" t="s">
+      <c r="O20" s="47"/>
+      <c r="P20" s="47"/>
+      <c r="Q20" s="18">
+        <f>SUM(Q8:Q19)</f>
+        <v>36.4893</v>
+      </c>
+      <c r="R20" s="1"/>
+    </row>
+    <row r="21" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="O19" s="44"/>
-      <c r="P19" s="44"/>
-      <c r="Q19" s="19">
-        <f>Q18/5</f>
-        <v>6.9719600000000002</v>
-      </c>
-      <c r="R19" s="1"/>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="M31" s="38"/>
+      <c r="O21" s="47"/>
+      <c r="P21" s="47"/>
+      <c r="Q21" s="19">
+        <f>Q20/5</f>
+        <v>7.29786</v>
+      </c>
+      <c r="R21" s="1"/>
+    </row>
+    <row r="33" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M33" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K1:R1"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="N21:P21"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O9" r:id="rId1"/>
@@ -1840,8 +1997,10 @@
     <hyperlink ref="O15" r:id="rId8"/>
     <hyperlink ref="O16" r:id="rId9"/>
     <hyperlink ref="O17" r:id="rId10"/>
+    <hyperlink ref="O18" r:id="rId11"/>
+    <hyperlink ref="O19" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId13"/>
 </worksheet>
 </file>